--- a/data/trans_orig/IP07A01-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07A01-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2007 (tasa de respuesta: 99,7%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma, percibida por el adulto en 2007 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14713</t>
+          <t>15030</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26274</t>
+          <t>25860</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17254</t>
+          <t>16876</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27418</t>
+          <t>27033</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34511</t>
+          <t>34112</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49660</t>
+          <t>49586</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,88%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19861</t>
+          <t>19810</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31393</t>
+          <t>30914</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11411</t>
+          <t>11647</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21468</t>
+          <t>21509</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34586</t>
+          <t>34560</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49972</t>
+          <t>50315</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>56,7%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t>4611</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>689</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6186</t>
+          <t>6093</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4388</t>
+          <t>4611</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>520</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10938</t>
+          <t>10505</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19417</t>
+          <t>19516</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10146</t>
+          <t>10185</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18834</t>
+          <t>18902</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23359</t>
+          <t>22951</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36110</t>
+          <t>36327</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,92%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>8248</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16483</t>
+          <t>16693</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11863</t>
+          <t>11680</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20723</t>
+          <t>20216</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21193</t>
+          <t>21537</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34604</t>
+          <t>34547</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,03%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>697</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>6341</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2498</t>
+          <t>2546</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2452</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>3207</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3999</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9630</t>
+          <t>9293</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18393</t>
+          <t>18124</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21159</t>
+          <t>21233</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32952</t>
+          <t>32538</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33133</t>
+          <t>32773</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48036</t>
+          <t>48411</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>55,3%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13423</t>
+          <t>13394</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22561</t>
+          <t>22544</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17755</t>
+          <t>17306</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29555</t>
+          <t>29036</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33867</t>
+          <t>33985</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49152</t>
+          <t>49720</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>56,8%</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>642</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>677</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>681</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6110</t>
+          <t>5711</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37844</t>
+          <t>38628</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53198</t>
+          <t>54013</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42813</t>
+          <t>43269</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>58764</t>
+          <t>58879</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>86467</t>
+          <t>86977</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>107784</t>
+          <t>107503</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,73%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30611</t>
+          <t>29918</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45475</t>
+          <t>44399</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>28520</t>
+          <t>28472</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>44369</t>
+          <t>43661</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>62281</t>
+          <t>62546</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>85146</t>
+          <t>82935</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>45,31%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>2646</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10387</t>
+          <t>10295</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9419</t>
+          <t>9022</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6083</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16200</t>
+          <t>16945</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4552</t>
+          <t>4477</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>577</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5139</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>3586</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>3344</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21071</t>
+          <t>20905</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>32715</t>
+          <t>32269</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>28749</t>
+          <t>29146</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>41947</t>
+          <t>42610</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>53539</t>
+          <t>53223</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>71641</t>
+          <t>72048</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,82%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13371</t>
+          <t>13616</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24755</t>
+          <t>25289</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>26931</t>
+          <t>26495</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>39922</t>
+          <t>39996</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>44119</t>
+          <t>42973</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>60909</t>
+          <t>61178</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>49,1%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3025</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11095</t>
+          <t>10841</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>3547</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>11809</t>
+          <t>13006</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>687</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6490</t>
+          <t>6673</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7182</t>
+          <t>5992</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2973</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>16030</t>
+          <t>15482</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>26513</t>
+          <t>25806</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>12788</t>
+          <t>12457</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>22069</t>
+          <t>21958</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>31388</t>
+          <t>31766</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>45229</t>
+          <t>45338</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,39%</t>
         </is>
       </c>
     </row>
@@ -4256,12 +4256,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>11491</t>
+          <t>12049</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>21539</t>
+          <t>22142</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4271,12 +4271,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4291,12 +4291,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10445</t>
+          <t>9775</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19278</t>
+          <t>19094</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>24297</t>
+          <t>24327</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>37906</t>
+          <t>38315</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>49,35%</t>
         </is>
       </c>
     </row>
@@ -4369,12 +4369,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>784</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6820</t>
+          <t>6866</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7846</t>
+          <t>7268</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3334</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>11382</t>
+          <t>11606</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4557,7 +4557,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>129731</t>
+          <t>129396</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>157158</t>
+          <t>156376</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>152366</t>
+          <t>152169</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>181256</t>
+          <t>181168</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>292497</t>
+          <t>287137</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>332046</t>
+          <t>330565</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,04%</t>
         </is>
       </c>
     </row>
@@ -4938,12 +4938,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>115160</t>
+          <t>115408</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>141338</t>
+          <t>141419</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4953,12 +4953,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4973,12 +4973,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>125788</t>
+          <t>125583</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>153753</t>
+          <t>153748</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5008,12 +5008,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>249397</t>
+          <t>246973</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>288391</t>
+          <t>289615</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5023,12 +5023,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,47%</t>
         </is>
       </c>
     </row>
@@ -5051,12 +5051,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>12382</t>
+          <t>12936</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>26274</t>
+          <t>27096</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>8874</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>20365</t>
+          <t>19405</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>24294</t>
+          <t>24577</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>42556</t>
+          <t>43175</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -5164,12 +5164,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2431</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>9726</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>10150</t>
+          <t>10344</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5214,12 +5214,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>5959</t>
+          <t>6347</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>16207</t>
+          <t>16587</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5249,12 +5249,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>5595</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6117</t>
+          <t>6397</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5546,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2012 (tasa de respuesta: 98,12%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma, percibida por el adulto en 2012 (tasa de respuesta: 98,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5741,12 +5741,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10457</t>
+          <t>10281</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20719</t>
+          <t>20512</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5756,12 +5756,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7419</t>
+          <t>7266</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16802</t>
+          <t>16641</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20391</t>
+          <t>20313</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33511</t>
+          <t>33750</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,37%</t>
         </is>
       </c>
     </row>
@@ -5854,12 +5854,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11739</t>
+          <t>11419</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21734</t>
+          <t>21800</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5889,12 +5889,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15240</t>
+          <t>15526</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25034</t>
+          <t>24918</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29344</t>
+          <t>29537</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43507</t>
+          <t>43666</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,7%</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>4274</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12030</t>
+          <t>12456</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>701</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>5987</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6170</t>
+          <t>6045</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16656</t>
+          <t>16167</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>21,73%</t>
         </is>
       </c>
     </row>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3684</t>
+          <t>4044</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3768</t>
+          <t>5856</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -6423,12 +6423,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7072</t>
+          <t>7058</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16193</t>
+          <t>16333</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6438,12 +6438,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6458,12 +6458,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>8411</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16966</t>
+          <t>17004</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17645</t>
+          <t>17650</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31100</t>
+          <t>30202</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>43,68%</t>
         </is>
       </c>
     </row>
@@ -6536,12 +6536,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15742</t>
+          <t>16378</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25378</t>
+          <t>26039</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16942</t>
+          <t>16565</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25841</t>
+          <t>25561</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35339</t>
+          <t>36113</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48775</t>
+          <t>48791</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,56%</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>3175</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -6767,7 +6767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>4373</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -7105,12 +7105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>7952</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17719</t>
+          <t>17753</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12481</t>
+          <t>12922</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21647</t>
+          <t>21950</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23286</t>
+          <t>23415</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36989</t>
+          <t>37525</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>49,16%</t>
         </is>
       </c>
     </row>
@@ -7218,12 +7218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26064</t>
+          <t>25846</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35659</t>
+          <t>35589</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7964</t>
+          <t>7983</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16746</t>
+          <t>16470</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36004</t>
+          <t>35690</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50022</t>
+          <t>49583</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>64,96%</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3817</t>
+          <t>3862</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6443</t>
+          <t>6130</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7109</t>
+          <t>7578</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -7787,12 +7787,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25537</t>
+          <t>26382</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40996</t>
+          <t>40686</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28970</t>
+          <t>29665</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45119</t>
+          <t>45667</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>59186</t>
+          <t>60049</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80656</t>
+          <t>81786</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>43,74%</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>39655</t>
+          <t>39376</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>53941</t>
+          <t>53978</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>46633</t>
+          <t>46241</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>63788</t>
+          <t>62404</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>89843</t>
+          <t>90139</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>112667</t>
+          <t>112715</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>60,28%</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2482</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10010</t>
+          <t>9826</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>1431</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8284</t>
+          <t>9475</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15256</t>
+          <t>15435</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9373</t>
+          <t>9740</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3820</t>
+          <t>4364</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>18484</t>
+          <t>18188</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>31715</t>
+          <t>31694</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>22294</t>
+          <t>22175</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>35910</t>
+          <t>36502</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>44309</t>
+          <t>44740</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>63365</t>
+          <t>64386</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>43,46%</t>
         </is>
       </c>
     </row>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>41127</t>
+          <t>41319</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>54877</t>
+          <t>54814</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>30564</t>
+          <t>30469</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>44367</t>
+          <t>44776</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>75911</t>
+          <t>75767</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>95786</t>
+          <t>95743</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,63%</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>691</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6680</t>
+          <t>7232</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7868</t>
+          <t>7420</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>11320</t>
+          <t>10601</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -8843,12 +8843,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>426</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5679</t>
+          <t>5540</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8863,7 +8863,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>427</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>5394</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4597</t>
+          <t>4261</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>11704</t>
+          <t>11916</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>14564</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>24871</t>
+          <t>25000</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>20445</t>
+          <t>20421</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>33389</t>
+          <t>33271</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,41%</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>11497</t>
+          <t>11352</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>19317</t>
+          <t>19388</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>9153</t>
+          <t>9028</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19001</t>
+          <t>18940</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>23033</t>
+          <t>23253</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>36277</t>
+          <t>36141</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,02%</t>
         </is>
       </c>
     </row>
@@ -9382,7 +9382,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3421</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>594</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5578</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6820</t>
+          <t>6868</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9530,7 +9530,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4364</t>
+          <t>4341</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -9643,57 +9643,57 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
+          <t>3012</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>8,05%</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
           <t>3092</t>
         </is>
       </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>8,26%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>3264</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>92282</t>
+          <t>91729</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>118353</t>
+          <t>119679</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>114478</t>
+          <t>113733</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>141927</t>
+          <t>141505</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>215123</t>
+          <t>213840</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>254278</t>
+          <t>253420</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,05%</t>
         </is>
       </c>
     </row>
@@ -9946,12 +9946,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>165011</t>
+          <t>164047</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>193276</t>
+          <t>192318</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9981,12 +9981,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>144573</t>
+          <t>144096</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>173604</t>
+          <t>173175</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>317407</t>
+          <t>318279</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>357867</t>
+          <t>358630</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>58,1%</t>
         </is>
       </c>
     </row>
@@ -10059,12 +10059,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>11939</t>
+          <t>11997</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>26195</t>
+          <t>25082</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>9715</t>
+          <t>10307</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>22721</t>
+          <t>23249</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>25003</t>
+          <t>24718</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>43721</t>
+          <t>42621</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -10172,12 +10172,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1645</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>8823</t>
+          <t>9523</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>12277</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>6647</t>
+          <t>6740</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>17723</t>
+          <t>18178</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -10320,47 +10320,47 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>6470</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>2559</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
           <t>636</t>
         </is>
       </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>5914</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>2559</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>6461</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -10554,7 +10554,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2016 (tasa de respuesta: 99,02%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma, percibida por el adulto en 2016 (tasa de respuesta: 99,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10749,12 +10749,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13908</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22649</t>
+          <t>23180</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10764,12 +10764,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16743</t>
+          <t>17667</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27140</t>
+          <t>27848</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10799,12 +10799,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10819,12 +10819,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33470</t>
+          <t>33172</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47284</t>
+          <t>47814</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>65,58%</t>
         </is>
       </c>
     </row>
@@ -10862,12 +10862,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10344</t>
+          <t>10569</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20014</t>
+          <t>19679</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10877,12 +10877,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>8675</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18399</t>
+          <t>18323</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10912,12 +10912,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10932,12 +10932,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21623</t>
+          <t>21729</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35169</t>
+          <t>35637</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10947,12 +10947,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,88%</t>
         </is>
       </c>
     </row>
@@ -11010,12 +11010,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>635</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5886</t>
+          <t>6035</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11025,12 +11025,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11045,12 +11045,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>637</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6041</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4356</t>
+          <t>4883</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11108,7 +11108,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11178,7 +11178,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -11431,12 +11431,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15003</t>
+          <t>15167</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26504</t>
+          <t>26727</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11446,12 +11446,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11466,12 +11466,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24761</t>
+          <t>24901</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35748</t>
+          <t>36205</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11481,12 +11481,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11501,12 +11501,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43039</t>
+          <t>42989</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60394</t>
+          <t>58918</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>58,38%</t>
         </is>
       </c>
     </row>
@@ -11544,12 +11544,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22132</t>
+          <t>22280</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34088</t>
+          <t>34288</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11559,12 +11559,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11579,12 +11579,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11393</t>
+          <t>10958</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22470</t>
+          <t>22161</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11594,12 +11594,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11614,12 +11614,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35315</t>
+          <t>36863</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52736</t>
+          <t>52926</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11629,12 +11629,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>52,44%</t>
         </is>
       </c>
     </row>
@@ -11657,12 +11657,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>920</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>7424</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11672,12 +11672,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2872</t>
+          <t>3518</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11727,12 +11727,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9028</t>
+          <t>8532</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3816</t>
+          <t>3419</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11790,7 +11790,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11810,7 +11810,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3937</t>
+          <t>4317</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11825,7 +11825,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11845,7 +11845,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4630</t>
+          <t>5018</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11860,7 +11860,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -12113,12 +12113,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12188</t>
+          <t>12429</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20457</t>
+          <t>21207</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12128,12 +12128,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12148,12 +12148,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15854</t>
+          <t>15453</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26874</t>
+          <t>26377</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12163,47 +12163,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
+          <t>64,33%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>37838</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>31631</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>45291</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>54,75%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>45,77%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>65,54%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>37838</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>30638</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>44441</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>54,75%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>44,33%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>64,31%</t>
         </is>
       </c>
     </row>
@@ -12226,12 +12226,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6616</t>
+          <t>6025</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14809</t>
+          <t>14461</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12241,12 +12241,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12261,12 +12261,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10735</t>
+          <t>10326</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21143</t>
+          <t>21047</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12296,12 +12296,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19520</t>
+          <t>18845</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32742</t>
+          <t>32418</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>46,91%</t>
         </is>
       </c>
     </row>
@@ -12374,12 +12374,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>660</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>6092</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12409,12 +12409,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>646</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -12457,7 +12457,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6529</t>
+          <t>5486</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12522,12 +12522,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>621</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6715</t>
+          <t>6403</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12537,12 +12537,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -12570,7 +12570,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12640,7 +12640,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12655,7 +12655,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -12795,12 +12795,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51129</t>
+          <t>50992</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>69338</t>
+          <t>69694</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>50921</t>
+          <t>50771</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67801</t>
+          <t>67495</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12865,12 +12865,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>108764</t>
+          <t>107810</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>131583</t>
+          <t>132007</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,37%</t>
         </is>
       </c>
     </row>
@@ -12908,12 +12908,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>38536</t>
+          <t>38017</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>56020</t>
+          <t>55652</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>31737</t>
+          <t>31233</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>48256</t>
+          <t>48705</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12978,12 +12978,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>74600</t>
+          <t>74792</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>98621</t>
+          <t>99251</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12993,12 +12993,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,39%</t>
         </is>
       </c>
     </row>
@@ -13021,12 +13021,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10227</t>
+          <t>11261</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13036,12 +13036,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>758</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7992</t>
+          <t>8177</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13076,7 +13076,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13091,12 +13091,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>14947</t>
+          <t>14675</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13106,12 +13106,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -13139,7 +13139,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13154,7 +13154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>5815</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13189,7 +13189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13204,12 +13204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>726</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6689</t>
+          <t>7648</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -13252,7 +13252,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13267,7 +13267,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13322,7 +13322,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13337,7 +13337,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -13477,12 +13477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>31938</t>
+          <t>32649</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>46565</t>
+          <t>47352</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13492,12 +13492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13512,12 +13512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>34165</t>
+          <t>34417</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>48701</t>
+          <t>48594</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13527,12 +13527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13547,12 +13547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>71208</t>
+          <t>70395</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>92029</t>
+          <t>91339</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13562,12 +13562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,06%</t>
         </is>
       </c>
     </row>
@@ -13590,12 +13590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>22859</t>
+          <t>22454</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>37057</t>
+          <t>36702</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13605,12 +13605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13625,12 +13625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>18649</t>
+          <t>18523</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32104</t>
+          <t>33146</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13640,12 +13640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13660,12 +13660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>44811</t>
+          <t>45237</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>64603</t>
+          <t>64924</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13675,12 +13675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,4%</t>
         </is>
       </c>
     </row>
@@ -13703,12 +13703,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>2296</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11071</t>
+          <t>11242</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13718,12 +13718,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13738,12 +13738,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13753,12 +13753,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13773,12 +13773,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4802</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>15225</t>
+          <t>15444</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -13821,7 +13821,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5086</t>
+          <t>5835</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13836,7 +13836,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13851,12 +13851,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>641</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6616</t>
+          <t>6384</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13866,12 +13866,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13886,12 +13886,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8434</t>
+          <t>8327</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -13969,7 +13969,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3428</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13984,7 +13984,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14004,7 +14004,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3464</t>
+          <t>4180</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14019,7 +14019,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>12341</t>
+          <t>12370</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>21435</t>
+          <t>21451</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14174,12 +14174,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14194,12 +14194,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>20107</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>30142</t>
+          <t>29898</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14209,12 +14209,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14229,12 +14229,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>35110</t>
+          <t>35512</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>49510</t>
+          <t>49009</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>69,17%</t>
         </is>
       </c>
     </row>
@@ -14272,12 +14272,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>8173</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>17208</t>
+          <t>16962</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14287,12 +14287,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14307,12 +14307,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7223</t>
+          <t>7220</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>16527</t>
+          <t>16831</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14322,12 +14322,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14342,12 +14342,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>18189</t>
+          <t>17906</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>32361</t>
+          <t>31062</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>43,84%</t>
         </is>
       </c>
     </row>
@@ -14390,7 +14390,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5927</t>
+          <t>6261</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14405,7 +14405,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14425,7 +14425,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4577</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14440,7 +14440,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14455,12 +14455,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>972</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8146</t>
+          <t>8012</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -14616,7 +14616,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>3951</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14631,7 +14631,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14686,7 +14686,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4745</t>
+          <t>5741</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14701,7 +14701,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -14841,12 +14841,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>155604</t>
+          <t>156997</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>187640</t>
+          <t>187882</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14856,12 +14856,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14876,12 +14876,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>186679</t>
+          <t>185431</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>218047</t>
+          <t>216365</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14891,12 +14891,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14911,12 +14911,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>352984</t>
+          <t>353403</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>395669</t>
+          <t>395013</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>57,92%</t>
         </is>
       </c>
     </row>
@@ -14954,12 +14954,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>126117</t>
+          <t>126525</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>157396</t>
+          <t>158070</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14969,12 +14969,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14989,12 +14989,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>106567</t>
+          <t>106867</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>137234</t>
+          <t>137302</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15004,12 +15004,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15024,12 +15024,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>242657</t>
+          <t>243595</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>285672</t>
+          <t>284226</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15039,12 +15039,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,67%</t>
         </is>
       </c>
     </row>
@@ -15067,12 +15067,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>10234</t>
+          <t>10410</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>24203</t>
+          <t>23112</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15082,12 +15082,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15102,12 +15102,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>9105</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>21418</t>
+          <t>21999</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15117,12 +15117,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15137,12 +15137,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>22141</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>40974</t>
+          <t>40427</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15152,12 +15152,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -15180,12 +15180,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2586</t>
+          <t>2735</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>10263</t>
+          <t>10957</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15195,12 +15195,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15215,12 +15215,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2464</t>
+          <t>2484</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>12271</t>
+          <t>12269</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15250,12 +15250,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>6705</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>18478</t>
+          <t>19179</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15270,7 +15270,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -15293,12 +15293,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>612</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5635</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15313,7 +15313,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15333,7 +15333,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15348,7 +15348,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15363,12 +15363,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>785</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6776</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15383,7 +15383,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -15562,7 +15562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma, percibida por el adulto en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -15757,12 +15757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28726</t>
+          <t>28992</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42152</t>
+          <t>42169</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -15772,12 +15772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -15792,12 +15792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43357</t>
+          <t>42359</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65301</t>
+          <t>65227</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -15807,12 +15807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -15827,12 +15827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77435</t>
+          <t>77840</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102931</t>
+          <t>102603</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -15842,12 +15842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,44%</t>
         </is>
       </c>
     </row>
@@ -15870,12 +15870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14732</t>
+          <t>14080</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27335</t>
+          <t>27507</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -15885,12 +15885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -15905,12 +15905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10044</t>
+          <t>10166</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23805</t>
+          <t>23928</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -15920,12 +15920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -15940,12 +15940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27570</t>
+          <t>26946</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47033</t>
+          <t>47900</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -15955,12 +15955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -15988,7 +15988,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4719</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -16003,7 +16003,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -16018,12 +16018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>2694</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26123</t>
+          <t>27520</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -16033,12 +16033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -16053,12 +16053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>4338</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31735</t>
+          <t>31577</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -16214,7 +16214,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -16229,7 +16229,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -16284,7 +16284,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -16299,7 +16299,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -16439,12 +16439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26234</t>
+          <t>25892</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39182</t>
+          <t>38705</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -16454,12 +16454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -16474,12 +16474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28398</t>
+          <t>28082</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41055</t>
+          <t>41125</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -16489,12 +16489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -16509,12 +16509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59884</t>
+          <t>58929</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77098</t>
+          <t>76398</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,06%</t>
         </is>
       </c>
     </row>
@@ -16552,12 +16552,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11388</t>
+          <t>11666</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22905</t>
+          <t>23335</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -16567,12 +16567,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -16587,12 +16587,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11831</t>
+          <t>12076</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23927</t>
+          <t>24379</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -16602,12 +16602,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -16622,12 +16622,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25614</t>
+          <t>25784</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>42887</t>
+          <t>42806</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,26%</t>
         </is>
       </c>
     </row>
@@ -16665,12 +16665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>548</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>6036</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -16680,12 +16680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -16705,7 +16705,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6141</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -16735,12 +16735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8497</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -16755,7 +16755,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -16778,12 +16778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>745</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7223</t>
+          <t>6934</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -16793,12 +16793,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -16848,12 +16848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>731</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7379</t>
+          <t>7307</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -16868,7 +16868,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -17121,12 +17121,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15924</t>
+          <t>15680</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24667</t>
+          <t>24446</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -17136,12 +17136,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -17156,12 +17156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22482</t>
+          <t>21832</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30950</t>
+          <t>31126</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -17171,12 +17171,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -17191,12 +17191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41591</t>
+          <t>41213</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53829</t>
+          <t>53440</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>81,68%</t>
         </is>
       </c>
     </row>
@@ -17234,12 +17234,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>5364</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13982</t>
+          <t>13640</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -17249,12 +17249,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -17269,12 +17269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2491</t>
+          <t>2366</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10305</t>
+          <t>9862</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -17304,12 +17304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9544</t>
+          <t>9340</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21204</t>
+          <t>21094</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -17319,12 +17319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,24%</t>
         </is>
       </c>
     </row>
@@ -17387,7 +17387,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6734</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -17422,7 +17422,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6262</t>
+          <t>6978</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -17437,7 +17437,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -17465,7 +17465,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>3664</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -17480,7 +17480,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -17535,7 +17535,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4667</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -17550,7 +17550,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -17803,12 +17803,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>63702</t>
+          <t>63825</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>99615</t>
+          <t>99979</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -17818,12 +17818,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -17838,12 +17838,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>57488</t>
+          <t>57878</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>81827</t>
+          <t>81581</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -17853,12 +17853,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -17873,12 +17873,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>128793</t>
+          <t>128704</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>177994</t>
+          <t>178485</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>74,46%</t>
         </is>
       </c>
     </row>
@@ -17916,12 +17916,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17006</t>
+          <t>15796</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>49631</t>
+          <t>48871</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -17931,12 +17931,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -17951,12 +17951,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>30109</t>
+          <t>30901</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>53850</t>
+          <t>54604</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -17966,12 +17966,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -17986,12 +17986,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>49668</t>
+          <t>51947</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>95220</t>
+          <t>95763</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -18001,12 +18001,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,95%</t>
         </is>
       </c>
     </row>
@@ -18029,12 +18029,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>705</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7478</t>
+          <t>7387</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -18064,12 +18064,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2789</t>
+          <t>2502</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14115</t>
+          <t>13243</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -18079,12 +18079,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5164</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>18470</t>
+          <t>18035</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -18114,12 +18114,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -18147,7 +18147,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>4371</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -18162,7 +18162,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -18177,12 +18177,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>501</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6723</t>
+          <t>6635</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -18192,12 +18192,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -18212,12 +18212,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>765</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>7839</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -18227,12 +18227,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -18260,7 +18260,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>2696</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -18275,7 +18275,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -18295,7 +18295,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6504</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -18310,7 +18310,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -18330,7 +18330,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>5558</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -18345,7 +18345,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -18485,12 +18485,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>35168</t>
+          <t>35142</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>48119</t>
+          <t>48150</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -18500,12 +18500,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -18520,12 +18520,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>47648</t>
+          <t>49038</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>69396</t>
+          <t>71136</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -18535,12 +18535,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -18555,12 +18555,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>87460</t>
+          <t>87382</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>113460</t>
+          <t>113684</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,12%</t>
         </is>
       </c>
     </row>
@@ -18598,12 +18598,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13779</t>
+          <t>13613</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26299</t>
+          <t>26025</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -18613,12 +18613,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -18633,12 +18633,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>18741</t>
+          <t>16450</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>38634</t>
+          <t>36481</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -18648,12 +18648,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -18668,12 +18668,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>35654</t>
+          <t>35660</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>59891</t>
+          <t>59205</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -18683,12 +18683,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,08%</t>
         </is>
       </c>
     </row>
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>380</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5282</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -18726,12 +18726,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -18746,12 +18746,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>926</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7304</t>
+          <t>7067</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -18761,12 +18761,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -18781,12 +18781,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>2273</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9667</t>
+          <t>9783</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -18796,12 +18796,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>581</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>6813</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -18874,12 +18874,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -18894,12 +18894,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>603</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -18909,12 +18909,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -18977,7 +18977,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>5487</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -18992,7 +18992,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -19027,7 +19027,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -19167,12 +19167,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>16901</t>
+          <t>17736</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>28201</t>
+          <t>28675</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -19182,12 +19182,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -19202,12 +19202,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>19997</t>
+          <t>20096</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>33097</t>
+          <t>33297</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -19217,12 +19217,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -19237,12 +19237,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>42128</t>
+          <t>41400</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>58627</t>
+          <t>58306</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -19252,12 +19252,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>66,61%</t>
         </is>
       </c>
     </row>
@@ -19280,12 +19280,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>10534</t>
+          <t>9724</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>21562</t>
+          <t>20242</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -19295,12 +19295,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -19315,12 +19315,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10993</t>
+          <t>10660</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>22804</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -19330,12 +19330,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -19350,12 +19350,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>22848</t>
+          <t>23220</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>39449</t>
+          <t>40153</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -19365,12 +19365,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,87%</t>
         </is>
       </c>
     </row>
@@ -19428,12 +19428,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>723</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7096</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -19443,12 +19443,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -19463,12 +19463,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>747</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>6776</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -19483,7 +19483,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -19511,7 +19511,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -19526,7 +19526,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -19546,7 +19546,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -19561,7 +19561,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -19576,12 +19576,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>651</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>7826</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -19591,12 +19591,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -19624,7 +19624,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4189</t>
+          <t>4380</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -19639,7 +19639,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -19694,7 +19694,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4612</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -19709,7 +19709,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -19849,12 +19849,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>213480</t>
+          <t>214745</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>262527</t>
+          <t>266339</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -19884,12 +19884,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>252521</t>
+          <t>252899</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>297830</t>
+          <t>299040</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -19899,12 +19899,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -19919,12 +19919,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>477128</t>
+          <t>477073</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>546168</t>
+          <t>544340</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -19934,12 +19934,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,14%</t>
         </is>
       </c>
     </row>
@@ -19962,12 +19962,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>89701</t>
+          <t>87491</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>134992</t>
+          <t>134275</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -19977,12 +19977,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -19997,12 +19997,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>105596</t>
+          <t>105697</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>144149</t>
+          <t>143741</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -20012,12 +20012,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -20032,12 +20032,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>209116</t>
+          <t>210165</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>267484</t>
+          <t>266958</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -20047,12 +20047,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,42%</t>
         </is>
       </c>
     </row>
@@ -20075,12 +20075,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>4416</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>14393</t>
+          <t>14011</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -20090,12 +20090,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -20110,12 +20110,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>17460</t>
+          <t>16365</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>47995</t>
+          <t>45912</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -20125,12 +20125,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -20145,12 +20145,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>23984</t>
+          <t>23697</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>53169</t>
+          <t>55506</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -20160,12 +20160,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -20188,12 +20188,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2298</t>
+          <t>2589</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>12875</t>
+          <t>12866</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -20203,12 +20203,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -20223,12 +20223,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2685</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>11185</t>
+          <t>11239</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -20243,7 +20243,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -20258,12 +20258,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>6428</t>
+          <t>6793</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>19256</t>
+          <t>18947</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -20273,12 +20273,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -20301,12 +20301,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>486</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>6158</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -20316,12 +20316,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -20341,7 +20341,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>6435</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -20356,7 +20356,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -20371,12 +20371,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1538</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>9444</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -20386,12 +20386,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
